--- a/public/raw/match3(BiratangaKingsvsPokharaAvengers)/match3(BiratangaKingsvsPokharaAvengers).xlsx
+++ b/public/raw/match3(BiratangaKingsvsPokharaAvengers)/match3(BiratangaKingsvsPokharaAvengers).xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5693" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5693" uniqueCount="958">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -883,6 +883,9 @@
     <t xml:space="preserve">Internet Services</t>
   </si>
   <si>
+    <t xml:space="preserve">ISP Service Provider</t>
+  </si>
+  <si>
     <t xml:space="preserve">Services</t>
   </si>
   <si>
@@ -913,9 +916,15 @@
     <t xml:space="preserve">16:21:42</t>
   </si>
   <si>
+    <t xml:space="preserve">Sonam Thermals</t>
+  </si>
+  <si>
     <t xml:space="preserve">Clothing</t>
   </si>
   <si>
+    <t xml:space="preserve">Thermals &amp; Jackets</t>
+  </si>
+  <si>
     <t xml:space="preserve">16:21:53</t>
   </si>
   <si>
@@ -2803,12 +2812,6 @@
     <t xml:space="preserve">19:25:12</t>
   </si>
   <si>
-    <t xml:space="preserve">Services-ISP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISP Service Provider</t>
-  </si>
-  <si>
     <t xml:space="preserve">19:26:14</t>
   </si>
   <si>
@@ -2822,12 +2825,6 @@
   </si>
   <si>
     <t xml:space="preserve">19:26:51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sonam Thermals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thermals &amp; Jackets</t>
   </si>
   <si>
     <t xml:space="preserve">19:28:43</t>
@@ -8382,10 +8379,10 @@
         <v>286</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J148" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L148" s="0" t="s">
         <v>42</v>
@@ -8399,10 +8396,10 @@
         <v>13</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D149" s="0" t="s">
         <v>85</v>
@@ -8437,10 +8434,10 @@
         <v>13</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D150" s="0" t="s">
         <v>25</v>
@@ -8472,10 +8469,10 @@
         <v>13</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D151" s="0" t="s">
         <v>97</v>
@@ -8507,10 +8504,10 @@
         <v>13</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D152" s="0" t="s">
         <v>74</v>
@@ -8542,10 +8539,10 @@
         <v>13</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D153" s="0" t="s">
         <v>62</v>
@@ -8577,10 +8574,10 @@
         <v>13</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D154" s="0" t="s">
         <v>72</v>
@@ -8612,13 +8609,13 @@
         <v>13</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D155" s="0" t="s">
-        <v>123</v>
+        <v>298</v>
       </c>
       <c r="E155" s="0" t="n">
         <v>5</v>
@@ -8630,10 +8627,10 @@
         <v>18</v>
       </c>
       <c r="H155" s="0" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>123</v>
+        <v>300</v>
       </c>
       <c r="J155" s="0" t="s">
         <v>34</v>
@@ -8650,10 +8647,10 @@
         <v>13</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D156" s="0" t="s">
         <v>40</v>
@@ -8688,10 +8685,10 @@
         <v>13</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D157" s="0" t="s">
         <v>120</v>
@@ -8726,10 +8723,10 @@
         <v>13</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D158" s="0" t="s">
         <v>184</v>
@@ -8764,10 +8761,10 @@
         <v>13</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D159" s="0" t="s">
         <v>25</v>
@@ -8802,10 +8799,10 @@
         <v>13</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D160" s="0" t="s">
         <v>168</v>
@@ -8837,10 +8834,10 @@
         <v>13</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D161" s="0" t="s">
         <v>184</v>
@@ -8872,10 +8869,10 @@
         <v>13</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D162" s="0" t="s">
         <v>25</v>
@@ -8907,10 +8904,10 @@
         <v>13</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D163" s="0" t="s">
         <v>62</v>
@@ -8942,10 +8939,10 @@
         <v>13</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D164" s="0" t="s">
         <v>67</v>
@@ -8977,10 +8974,10 @@
         <v>13</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D165" s="0" t="s">
         <v>55</v>
@@ -9015,10 +9012,10 @@
         <v>13</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D166" s="0" t="s">
         <v>97</v>
@@ -9050,10 +9047,10 @@
         <v>13</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D167" s="0" t="s">
         <v>107</v>
@@ -9085,13 +9082,13 @@
         <v>13</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D168" s="0" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E168" s="0" t="n">
         <v>19</v>
@@ -9120,10 +9117,10 @@
         <v>13</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D169" s="0" t="s">
         <v>25</v>
@@ -9155,10 +9152,10 @@
         <v>13</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D170" s="0" t="s">
         <v>25</v>
@@ -9193,10 +9190,10 @@
         <v>13</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D171" s="0" t="s">
         <v>25</v>
@@ -9231,10 +9228,10 @@
         <v>13</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D172" s="0" t="s">
         <v>25</v>
@@ -9269,10 +9266,10 @@
         <v>13</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D173" s="0" t="s">
         <v>131</v>
@@ -9307,10 +9304,10 @@
         <v>13</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D174" s="0" t="s">
         <v>172</v>
@@ -9345,10 +9342,10 @@
         <v>13</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D175" s="0" t="s">
         <v>97</v>
@@ -9380,10 +9377,10 @@
         <v>13</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D176" s="0" t="s">
         <v>107</v>
@@ -9415,13 +9412,13 @@
         <v>13</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D177" s="0" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E177" s="0" t="n">
         <v>18</v>
@@ -9450,10 +9447,10 @@
         <v>13</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D178" s="0" t="s">
         <v>25</v>
@@ -9485,10 +9482,10 @@
         <v>13</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D179" s="0" t="s">
         <v>25</v>
@@ -9523,13 +9520,13 @@
         <v>13</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D180" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E180" s="0" t="n">
         <v>7</v>
@@ -9541,10 +9538,10 @@
         <v>18</v>
       </c>
       <c r="H180" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J180" s="0" t="s">
         <v>27</v>
@@ -9561,10 +9558,10 @@
         <v>13</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D181" s="0" t="s">
         <v>97</v>
@@ -9596,10 +9593,10 @@
         <v>13</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D182" s="0" t="s">
         <v>131</v>
@@ -9631,10 +9628,10 @@
         <v>13</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D183" s="0" t="s">
         <v>165</v>
@@ -9666,10 +9663,10 @@
         <v>13</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D184" s="0" t="s">
         <v>25</v>
@@ -9701,10 +9698,10 @@
         <v>13</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D185" s="0" t="s">
         <v>25</v>
@@ -9739,10 +9736,10 @@
         <v>13</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D186" s="0" t="s">
         <v>25</v>
@@ -9777,10 +9774,10 @@
         <v>13</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D187" s="0" t="s">
         <v>25</v>
@@ -9815,10 +9812,10 @@
         <v>13</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D188" s="0" t="s">
         <v>25</v>
@@ -9850,10 +9847,10 @@
         <v>13</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D189" s="0" t="s">
         <v>74</v>
@@ -9885,10 +9882,10 @@
         <v>13</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D190" s="0" t="s">
         <v>139</v>
@@ -9920,10 +9917,10 @@
         <v>13</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D191" s="0" t="s">
         <v>55</v>
@@ -9955,10 +9952,10 @@
         <v>13</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D192" s="0" t="s">
         <v>172</v>
@@ -9990,10 +9987,10 @@
         <v>13</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D193" s="0" t="s">
         <v>97</v>
@@ -10025,10 +10022,10 @@
         <v>13</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D194" s="0" t="s">
         <v>148</v>
@@ -10060,10 +10057,10 @@
         <v>13</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D195" s="0" t="s">
         <v>67</v>
@@ -10095,10 +10092,10 @@
         <v>13</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D196" s="0" t="s">
         <v>25</v>
@@ -10130,10 +10127,10 @@
         <v>13</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D197" s="0" t="s">
         <v>79</v>
@@ -10168,10 +10165,10 @@
         <v>13</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D198" s="0" t="s">
         <v>25</v>
@@ -10206,10 +10203,10 @@
         <v>13</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D199" s="0" t="s">
         <v>90</v>
@@ -10244,10 +10241,10 @@
         <v>13</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D200" s="0" t="s">
         <v>82</v>
@@ -10282,13 +10279,13 @@
         <v>13</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D201" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E201" s="0" t="n">
         <v>5</v>
@@ -10300,13 +10297,13 @@
         <v>18</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J201" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L201" s="0" t="s">
         <v>20</v>
@@ -10320,10 +10317,10 @@
         <v>13</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D202" s="0" t="s">
         <v>25</v>
@@ -10358,10 +10355,10 @@
         <v>13</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D203" s="0" t="s">
         <v>25</v>
@@ -10393,10 +10390,10 @@
         <v>13</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D204" s="0" t="s">
         <v>74</v>
@@ -10428,10 +10425,10 @@
         <v>13</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D205" s="0" t="s">
         <v>159</v>
@@ -10463,10 +10460,10 @@
         <v>13</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D206" s="0" t="s">
         <v>115</v>
@@ -10498,13 +10495,13 @@
         <v>13</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D207" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E207" s="0" t="n">
         <v>23</v>
@@ -10516,13 +10513,13 @@
         <v>18</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J207" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L207" s="0" t="s">
         <v>247</v>
@@ -10536,10 +10533,10 @@
         <v>13</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D208" s="0" t="s">
         <v>165</v>
@@ -10574,10 +10571,10 @@
         <v>13</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D209" s="0" t="s">
         <v>115</v>
@@ -10612,10 +10609,10 @@
         <v>13</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D210" s="0" t="s">
         <v>79</v>
@@ -10650,10 +10647,10 @@
         <v>13</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D211" s="0" t="s">
         <v>90</v>
@@ -10688,10 +10685,10 @@
         <v>13</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D212" s="0" t="s">
         <v>172</v>
@@ -10726,13 +10723,13 @@
         <v>13</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D213" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E213" s="0" t="n">
         <v>14</v>
@@ -10744,13 +10741,13 @@
         <v>18</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J213" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L213" s="0" t="s">
         <v>35</v>
@@ -10764,10 +10761,10 @@
         <v>13</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D214" s="0" t="s">
         <v>97</v>
@@ -10799,10 +10796,10 @@
         <v>13</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D215" s="0" t="s">
         <v>82</v>
@@ -10834,13 +10831,13 @@
         <v>13</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D216" s="0" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E216" s="0" t="n">
         <v>8</v>
@@ -10852,10 +10849,10 @@
         <v>59</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="J216" s="0" t="s">
         <v>27</v>
@@ -10869,10 +10866,10 @@
         <v>13</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D217" s="0" t="s">
         <v>172</v>
@@ -10904,10 +10901,10 @@
         <v>13</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D218" s="0" t="s">
         <v>25</v>
@@ -10939,13 +10936,13 @@
         <v>13</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D219" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E219" s="0" t="n">
         <v>6</v>
@@ -10957,13 +10954,13 @@
         <v>18</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J219" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L219" s="0" t="s">
         <v>20</v>
@@ -10977,10 +10974,10 @@
         <v>13</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D220" s="0" t="s">
         <v>25</v>
@@ -11015,13 +11012,13 @@
         <v>13</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D221" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E221" s="0" t="n">
         <v>12</v>
@@ -11033,13 +11030,13 @@
         <v>18</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J221" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L221" s="0" t="s">
         <v>35</v>
@@ -11053,10 +11050,10 @@
         <v>13</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D222" s="0" t="s">
         <v>260</v>
@@ -11080,7 +11077,7 @@
         <v>262</v>
       </c>
       <c r="L222" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M222" s="0" t="n">
         <v>1</v>
@@ -11091,10 +11088,10 @@
         <v>13</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D223" s="0" t="s">
         <v>115</v>
@@ -11129,10 +11126,10 @@
         <v>13</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D224" s="0" t="s">
         <v>25</v>
@@ -11164,10 +11161,10 @@
         <v>13</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D225" s="0" t="s">
         <v>74</v>
@@ -11199,10 +11196,10 @@
         <v>13</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D226" s="0" t="s">
         <v>107</v>
@@ -11234,10 +11231,10 @@
         <v>13</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D227" s="0" t="s">
         <v>72</v>
@@ -11269,10 +11266,10 @@
         <v>13</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D228" s="0" t="s">
         <v>175</v>
@@ -11304,10 +11301,10 @@
         <v>13</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D229" s="0" t="s">
         <v>82</v>
@@ -11339,10 +11336,10 @@
         <v>13</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D230" s="0" t="s">
         <v>139</v>
@@ -11374,10 +11371,10 @@
         <v>13</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D231" s="0" t="s">
         <v>55</v>
@@ -11409,13 +11406,13 @@
         <v>13</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D232" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E232" s="0" t="n">
         <v>15</v>
@@ -11427,10 +11424,10 @@
         <v>59</v>
       </c>
       <c r="H232" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="J232" s="0" t="s">
         <v>27</v>
@@ -11444,10 +11441,10 @@
         <v>13</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D233" s="0" t="s">
         <v>25</v>
@@ -11479,10 +11476,10 @@
         <v>13</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D234" s="0" t="s">
         <v>62</v>
@@ -11514,10 +11511,10 @@
         <v>13</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D235" s="0" t="s">
         <v>25</v>
@@ -11549,10 +11546,10 @@
         <v>13</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D236" s="0" t="s">
         <v>67</v>
@@ -11584,10 +11581,10 @@
         <v>13</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D237" s="0" t="s">
         <v>72</v>
@@ -11619,10 +11616,10 @@
         <v>13</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D238" s="0" t="s">
         <v>97</v>
@@ -11654,10 +11651,10 @@
         <v>13</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D239" s="0" t="s">
         <v>25</v>
@@ -11689,10 +11686,10 @@
         <v>13</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D240" s="0" t="s">
         <v>74</v>
@@ -11710,7 +11707,7 @@
         <v>75</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="J240" s="0" t="s">
         <v>77</v>
@@ -11724,10 +11721,10 @@
         <v>13</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D241" s="0" t="s">
         <v>120</v>
@@ -11759,10 +11756,10 @@
         <v>13</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D242" s="0" t="s">
         <v>25</v>
@@ -11794,10 +11791,10 @@
         <v>13</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D243" s="0" t="s">
         <v>25</v>
@@ -11829,10 +11826,10 @@
         <v>13</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D244" s="0" t="s">
         <v>74</v>
@@ -11850,7 +11847,7 @@
         <v>75</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="J244" s="0" t="s">
         <v>77</v>
@@ -11864,10 +11861,10 @@
         <v>13</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D245" s="0" t="s">
         <v>90</v>
@@ -11899,10 +11896,10 @@
         <v>13</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D246" s="0" t="s">
         <v>67</v>
@@ -11934,10 +11931,10 @@
         <v>13</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D247" s="0" t="s">
         <v>79</v>
@@ -11972,10 +11969,10 @@
         <v>13</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D248" s="0" t="s">
         <v>97</v>
@@ -12007,10 +12004,10 @@
         <v>13</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D249" s="0" t="s">
         <v>148</v>
@@ -12042,10 +12039,10 @@
         <v>13</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D250" s="0" t="s">
         <v>82</v>
@@ -12077,10 +12074,10 @@
         <v>13</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D251" s="0" t="s">
         <v>172</v>
@@ -12112,10 +12109,10 @@
         <v>13</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D252" s="0" t="s">
         <v>25</v>
@@ -12147,10 +12144,10 @@
         <v>13</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D253" s="0" t="s">
         <v>25</v>
@@ -12182,10 +12179,10 @@
         <v>13</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D254" s="0" t="s">
         <v>74</v>
@@ -12203,7 +12200,7 @@
         <v>75</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="J254" s="0" t="s">
         <v>77</v>
@@ -12217,13 +12214,13 @@
         <v>13</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D255" s="0" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E255" s="0" t="n">
         <v>4</v>
@@ -12252,10 +12249,10 @@
         <v>13</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D256" s="0" t="s">
         <v>40</v>
@@ -12273,7 +12270,7 @@
         <v>41</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="J256" s="0" t="s">
         <v>19</v>
@@ -12287,10 +12284,10 @@
         <v>13</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D257" s="0" t="s">
         <v>72</v>
@@ -12322,10 +12319,10 @@
         <v>13</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D258" s="0" t="s">
         <v>168</v>
@@ -12357,10 +12354,10 @@
         <v>13</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D259" s="0" t="s">
         <v>184</v>
@@ -12392,10 +12389,10 @@
         <v>13</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D260" s="0" t="s">
         <v>25</v>
@@ -12427,13 +12424,13 @@
         <v>13</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D261" s="0" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E261" s="0" t="n">
         <v>18</v>
@@ -12462,10 +12459,10 @@
         <v>13</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D262" s="0" t="s">
         <v>62</v>
@@ -12497,10 +12494,10 @@
         <v>13</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D263" s="0" t="s">
         <v>97</v>
@@ -12532,10 +12529,10 @@
         <v>13</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D264" s="0" t="s">
         <v>107</v>
@@ -12567,10 +12564,10 @@
         <v>13</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D265" s="0" t="s">
         <v>62</v>
@@ -12602,10 +12599,10 @@
         <v>13</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D266" s="0" t="s">
         <v>67</v>
@@ -12637,10 +12634,10 @@
         <v>13</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D267" s="0" t="s">
         <v>25</v>
@@ -12672,10 +12669,10 @@
         <v>13</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D268" s="0" t="s">
         <v>25</v>
@@ -12707,10 +12704,10 @@
         <v>13</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D269" s="0" t="s">
         <v>74</v>
@@ -12728,7 +12725,7 @@
         <v>75</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="J269" s="0" t="s">
         <v>77</v>
@@ -12742,10 +12739,10 @@
         <v>13</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D270" s="0" t="s">
         <v>82</v>
@@ -12777,10 +12774,10 @@
         <v>13</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D271" s="0" t="s">
         <v>139</v>
@@ -12812,10 +12809,10 @@
         <v>13</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D272" s="0" t="s">
         <v>55</v>
@@ -12847,10 +12844,10 @@
         <v>13</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D273" s="0" t="s">
         <v>90</v>
@@ -12882,10 +12879,10 @@
         <v>13</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D274" s="0" t="s">
         <v>168</v>
@@ -12917,10 +12914,10 @@
         <v>13</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D275" s="0" t="s">
         <v>184</v>
@@ -12952,10 +12949,10 @@
         <v>13</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="D276" s="0" t="s">
         <v>25</v>
@@ -12987,10 +12984,10 @@
         <v>13</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D277" s="0" t="s">
         <v>55</v>
@@ -13022,10 +13019,10 @@
         <v>13</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D278" s="0" t="s">
         <v>159</v>
@@ -13057,10 +13054,10 @@
         <v>13</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D279" s="0" t="s">
         <v>85</v>
@@ -13092,10 +13089,10 @@
         <v>13</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D280" s="0" t="s">
         <v>97</v>
@@ -13127,13 +13124,13 @@
         <v>13</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D281" s="0" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E281" s="0" t="n">
         <v>9</v>
@@ -13145,10 +13142,10 @@
         <v>59</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="J281" s="0" t="s">
         <v>57</v>
@@ -13162,10 +13159,10 @@
         <v>13</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D282" s="0" t="s">
         <v>74</v>
@@ -13183,7 +13180,7 @@
         <v>75</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="J282" s="0" t="s">
         <v>77</v>
@@ -13197,10 +13194,10 @@
         <v>13</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D283" s="0" t="s">
         <v>25</v>
@@ -13232,10 +13229,10 @@
         <v>13</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D284" s="0" t="s">
         <v>25</v>
@@ -13267,10 +13264,10 @@
         <v>13</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D285" s="0" t="s">
         <v>25</v>
@@ -13302,10 +13299,10 @@
         <v>13</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D286" s="0" t="s">
         <v>74</v>
@@ -13323,7 +13320,7 @@
         <v>75</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="J286" s="0" t="s">
         <v>77</v>
@@ -13337,10 +13334,10 @@
         <v>13</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D287" s="0" t="s">
         <v>85</v>
@@ -13372,13 +13369,13 @@
         <v>13</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D288" s="0" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E288" s="0" t="n">
         <v>9</v>
@@ -13390,13 +13387,13 @@
         <v>59</v>
       </c>
       <c r="H288" s="0" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J288" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M288" s="0" t="n">
         <v>1</v>
@@ -13407,10 +13404,10 @@
         <v>13</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D289" s="0" t="s">
         <v>97</v>
@@ -13442,10 +13439,10 @@
         <v>13</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D290" s="0" t="s">
         <v>107</v>
@@ -13477,10 +13474,10 @@
         <v>13</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D291" s="0" t="s">
         <v>148</v>
@@ -13512,10 +13509,10 @@
         <v>13</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D292" s="0" t="s">
         <v>82</v>
@@ -13547,10 +13544,10 @@
         <v>13</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D293" s="0" t="s">
         <v>175</v>
@@ -13582,10 +13579,10 @@
         <v>13</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D294" s="0" t="s">
         <v>25</v>
@@ -13617,10 +13614,10 @@
         <v>13</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D295" s="0" t="s">
         <v>168</v>
@@ -13652,10 +13649,10 @@
         <v>13</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D296" s="0" t="s">
         <v>184</v>
@@ -13687,10 +13684,10 @@
         <v>13</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D297" s="0" t="s">
         <v>25</v>
@@ -13722,10 +13719,10 @@
         <v>13</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D298" s="0" t="s">
         <v>175</v>
@@ -13757,13 +13754,13 @@
         <v>13</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D299" s="0" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E299" s="0" t="n">
         <v>8</v>
@@ -13778,7 +13775,7 @@
         <v>26</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="J299" s="0" t="s">
         <v>27</v>
@@ -13792,10 +13789,10 @@
         <v>13</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D300" s="0" t="s">
         <v>62</v>
@@ -13827,10 +13824,10 @@
         <v>13</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D301" s="0" t="s">
         <v>25</v>
@@ -13862,10 +13859,10 @@
         <v>13</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D302" s="0" t="s">
         <v>74</v>
@@ -13897,10 +13894,10 @@
         <v>13</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D303" s="0" t="s">
         <v>172</v>
@@ -13932,10 +13929,10 @@
         <v>13</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D304" s="0" t="s">
         <v>72</v>
@@ -13967,13 +13964,13 @@
         <v>13</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D305" s="0" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E305" s="0" t="n">
         <v>10</v>
@@ -13985,10 +13982,10 @@
         <v>59</v>
       </c>
       <c r="H305" s="0" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="J305" s="0" t="s">
         <v>65</v>
@@ -14002,10 +13999,10 @@
         <v>13</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D306" s="0" t="s">
         <v>79</v>
@@ -14040,10 +14037,10 @@
         <v>13</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D307" s="0" t="s">
         <v>67</v>
@@ -14078,10 +14075,10 @@
         <v>13</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D308" s="0" t="s">
         <v>67</v>
@@ -14116,10 +14113,10 @@
         <v>13</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D309" s="0" t="s">
         <v>25</v>
@@ -14154,10 +14151,10 @@
         <v>13</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D310" s="0" t="s">
         <v>79</v>
@@ -14192,13 +14189,13 @@
         <v>13</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D311" s="0" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E311" s="0" t="n">
         <v>3</v>
@@ -14210,10 +14207,10 @@
         <v>18</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="J311" s="0" t="s">
         <v>110</v>
@@ -14230,10 +14227,10 @@
         <v>13</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D312" s="0" t="s">
         <v>168</v>
@@ -14268,10 +14265,10 @@
         <v>13</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D313" s="0" t="s">
         <v>184</v>
@@ -14306,10 +14303,10 @@
         <v>13</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D314" s="0" t="s">
         <v>25</v>
@@ -14344,10 +14341,10 @@
         <v>13</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D315" s="0" t="s">
         <v>168</v>
@@ -14379,10 +14376,10 @@
         <v>13</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D316" s="0" t="s">
         <v>184</v>
@@ -14414,10 +14411,10 @@
         <v>13</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D317" s="0" t="s">
         <v>25</v>
@@ -14449,13 +14446,13 @@
         <v>13</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D318" s="0" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E318" s="0" t="n">
         <v>4</v>
@@ -14467,10 +14464,10 @@
         <v>59</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="J318" s="0" t="s">
         <v>19</v>
@@ -14484,10 +14481,10 @@
         <v>13</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D319" s="0" t="s">
         <v>67</v>
@@ -14522,10 +14519,10 @@
         <v>13</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D320" s="0" t="s">
         <v>184</v>
@@ -14560,10 +14557,10 @@
         <v>13</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D321" s="0" t="s">
         <v>25</v>
@@ -14598,13 +14595,13 @@
         <v>13</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D322" s="0" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E322" s="0" t="n">
         <v>35</v>
@@ -14616,16 +14613,16 @@
         <v>18</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="J322" s="0" t="s">
         <v>93</v>
       </c>
       <c r="L322" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M322" s="0" t="n">
         <v>1</v>
@@ -14636,10 +14633,10 @@
         <v>13</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D323" s="0" t="s">
         <v>62</v>
@@ -14663,7 +14660,7 @@
         <v>65</v>
       </c>
       <c r="L323" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M323" s="0" t="n">
         <v>1</v>
@@ -14674,13 +14671,13 @@
         <v>13</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D324" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E324" s="0" t="n">
         <v>6</v>
@@ -14692,13 +14689,13 @@
         <v>18</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J324" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L324" s="0" t="s">
         <v>20</v>
@@ -14712,10 +14709,10 @@
         <v>13</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D325" s="0" t="s">
         <v>168</v>
@@ -14747,10 +14744,10 @@
         <v>13</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D326" s="0" t="s">
         <v>184</v>
@@ -14782,10 +14779,10 @@
         <v>13</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D327" s="0" t="s">
         <v>25</v>
@@ -14817,13 +14814,13 @@
         <v>13</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D328" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E328" s="0" t="n">
         <v>15</v>
@@ -14835,10 +14832,10 @@
         <v>59</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="J328" s="0" t="s">
         <v>27</v>
@@ -14852,10 +14849,10 @@
         <v>13</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D329" s="0" t="s">
         <v>72</v>
@@ -14887,10 +14884,10 @@
         <v>13</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D330" s="0" t="s">
         <v>25</v>
@@ -14922,13 +14919,13 @@
         <v>13</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D331" s="0" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E331" s="0" t="n">
         <v>29</v>
@@ -14940,10 +14937,10 @@
         <v>59</v>
       </c>
       <c r="H331" s="0" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="J331" s="0" t="s">
         <v>65</v>
@@ -14957,10 +14954,10 @@
         <v>13</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D332" s="0" t="s">
         <v>67</v>
@@ -14992,10 +14989,10 @@
         <v>13</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D333" s="0" t="s">
         <v>72</v>
@@ -15027,10 +15024,10 @@
         <v>13</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D334" s="0" t="s">
         <v>97</v>
@@ -15062,10 +15059,10 @@
         <v>13</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="D335" s="0" t="s">
         <v>79</v>
@@ -15097,10 +15094,10 @@
         <v>13</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D336" s="0" t="s">
         <v>74</v>
@@ -15132,10 +15129,10 @@
         <v>13</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D337" s="0" t="s">
         <v>25</v>
@@ -15167,13 +15164,13 @@
         <v>13</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D338" s="0" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E338" s="0" t="n">
         <v>17</v>
@@ -15202,10 +15199,10 @@
         <v>13</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D339" s="0" t="s">
         <v>97</v>
@@ -15237,10 +15234,10 @@
         <v>13</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D340" s="0" t="s">
         <v>115</v>
@@ -15272,13 +15269,13 @@
         <v>13</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D341" s="0" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E341" s="0" t="n">
         <v>11</v>
@@ -15290,10 +15287,10 @@
         <v>59</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="J341" s="0" t="s">
         <v>65</v>
@@ -15307,10 +15304,10 @@
         <v>13</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D342" s="0" t="s">
         <v>25</v>
@@ -15342,10 +15339,10 @@
         <v>13</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D343" s="0" t="s">
         <v>97</v>
@@ -15377,10 +15374,10 @@
         <v>13</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D344" s="0" t="s">
         <v>107</v>
@@ -15412,10 +15409,10 @@
         <v>13</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="D345" s="0" t="s">
         <v>82</v>
@@ -15447,10 +15444,10 @@
         <v>13</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D346" s="0" t="s">
         <v>85</v>
@@ -15482,10 +15479,10 @@
         <v>13</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D347" s="0" t="s">
         <v>139</v>
@@ -15517,10 +15514,10 @@
         <v>13</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D348" s="0" t="s">
         <v>97</v>
@@ -15552,10 +15549,10 @@
         <v>13</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D349" s="0" t="s">
         <v>25</v>
@@ -15587,10 +15584,10 @@
         <v>13</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D350" s="0" t="s">
         <v>62</v>
@@ -15622,10 +15619,10 @@
         <v>13</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D351" s="0" t="s">
         <v>67</v>
@@ -15657,10 +15654,10 @@
         <v>13</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D352" s="0" t="s">
         <v>72</v>
@@ -15692,10 +15689,10 @@
         <v>13</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D353" s="0" t="s">
         <v>120</v>
@@ -15727,13 +15724,13 @@
         <v>13</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D354" s="0" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E354" s="0" t="n">
         <v>8</v>
@@ -15745,10 +15742,10 @@
         <v>59</v>
       </c>
       <c r="H354" s="0" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="J354" s="0" t="s">
         <v>27</v>
@@ -15762,13 +15759,13 @@
         <v>13</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D355" s="0" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E355" s="0" t="n">
         <v>10</v>
@@ -15780,10 +15777,10 @@
         <v>59</v>
       </c>
       <c r="H355" s="0" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="J355" s="0" t="s">
         <v>27</v>
@@ -15797,10 +15794,10 @@
         <v>13</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D356" s="0" t="s">
         <v>97</v>
@@ -15832,10 +15829,10 @@
         <v>13</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D357" s="0" t="s">
         <v>25</v>
@@ -15867,10 +15864,10 @@
         <v>13</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D358" s="0" t="s">
         <v>74</v>
@@ -15902,10 +15899,10 @@
         <v>13</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D359" s="0" t="s">
         <v>107</v>
@@ -15937,10 +15934,10 @@
         <v>13</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D360" s="0" t="s">
         <v>72</v>
@@ -15972,10 +15969,10 @@
         <v>13</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D361" s="0" t="s">
         <v>79</v>
@@ -16007,10 +16004,10 @@
         <v>13</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D362" s="0" t="s">
         <v>97</v>
@@ -16042,10 +16039,10 @@
         <v>13</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D363" s="0" t="s">
         <v>55</v>
@@ -16077,10 +16074,10 @@
         <v>13</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D364" s="0" t="s">
         <v>90</v>
@@ -16112,10 +16109,10 @@
         <v>13</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D365" s="0" t="s">
         <v>97</v>
@@ -16147,10 +16144,10 @@
         <v>13</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D366" s="0" t="s">
         <v>25</v>
@@ -16182,10 +16179,10 @@
         <v>13</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D367" s="0" t="s">
         <v>115</v>
@@ -16220,10 +16217,10 @@
         <v>13</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D368" s="0" t="s">
         <v>62</v>
@@ -16247,7 +16244,7 @@
         <v>65</v>
       </c>
       <c r="L368" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M368" s="0" t="n">
         <v>1</v>
@@ -16258,10 +16255,10 @@
         <v>13</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D369" s="0" t="s">
         <v>62</v>
@@ -16285,7 +16282,7 @@
         <v>65</v>
       </c>
       <c r="L369" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M369" s="0" t="n">
         <v>1</v>
@@ -16296,10 +16293,10 @@
         <v>13</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D370" s="0" t="s">
         <v>25</v>
@@ -16334,10 +16331,10 @@
         <v>13</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="D371" s="0" t="s">
         <v>97</v>
@@ -16372,13 +16369,13 @@
         <v>13</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D372" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E372" s="0" t="n">
         <v>3</v>
@@ -16390,13 +16387,13 @@
         <v>18</v>
       </c>
       <c r="H372" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I372" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J372" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L372" s="0" t="s">
         <v>20</v>
@@ -16410,13 +16407,13 @@
         <v>13</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D373" s="0" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E373" s="0" t="n">
         <v>5</v>
@@ -16428,10 +16425,10 @@
         <v>18</v>
       </c>
       <c r="H373" s="0" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I373" s="0" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="J373" s="0" t="s">
         <v>27</v>
@@ -16448,13 +16445,13 @@
         <v>13</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D374" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E374" s="0" t="n">
         <v>9</v>
@@ -16466,13 +16463,13 @@
         <v>18</v>
       </c>
       <c r="H374" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I374" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J374" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L374" s="0" t="s">
         <v>20</v>
@@ -16486,10 +16483,10 @@
         <v>13</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D375" s="0" t="s">
         <v>115</v>
@@ -16524,13 +16521,13 @@
         <v>13</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D376" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E376" s="0" t="n">
         <v>7</v>
@@ -16542,13 +16539,13 @@
         <v>18</v>
       </c>
       <c r="H376" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I376" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J376" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L376" s="0" t="s">
         <v>20</v>
@@ -16562,10 +16559,10 @@
         <v>13</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D377" s="0" t="s">
         <v>25</v>
@@ -16600,13 +16597,13 @@
         <v>13</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D378" s="0" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E378" s="0" t="n">
         <v>6</v>
@@ -16618,10 +16615,10 @@
         <v>18</v>
       </c>
       <c r="H378" s="0" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I378" s="0" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="J378" s="0" t="s">
         <v>65</v>
@@ -16638,10 +16635,10 @@
         <v>13</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D379" s="0" t="s">
         <v>25</v>
@@ -16673,10 +16670,10 @@
         <v>13</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D380" s="0" t="s">
         <v>97</v>
@@ -16708,10 +16705,10 @@
         <v>13</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D381" s="0" t="s">
         <v>79</v>
@@ -16743,10 +16740,10 @@
         <v>13</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D382" s="0" t="s">
         <v>74</v>
@@ -16778,10 +16775,10 @@
         <v>13</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D383" s="0" t="s">
         <v>62</v>
@@ -16813,10 +16810,10 @@
         <v>13</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D384" s="0" t="s">
         <v>72</v>
@@ -16848,10 +16845,10 @@
         <v>13</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="D385" s="0" t="s">
         <v>74</v>
@@ -16886,10 +16883,10 @@
         <v>13</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="D386" s="0" t="s">
         <v>120</v>
@@ -16924,10 +16921,10 @@
         <v>13</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D387" s="0" t="s">
         <v>79</v>
@@ -16962,10 +16959,10 @@
         <v>13</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="D388" s="0" t="s">
         <v>85</v>
@@ -17000,10 +16997,10 @@
         <v>13</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D389" s="0" t="s">
         <v>184</v>
@@ -17027,7 +17024,7 @@
         <v>93</v>
       </c>
       <c r="L389" s="0" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="M389" s="0" t="n">
         <v>1</v>
@@ -17038,10 +17035,10 @@
         <v>13</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="D390" s="0" t="s">
         <v>25</v>
@@ -17076,10 +17073,10 @@
         <v>13</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D391" s="0" t="s">
         <v>115</v>
@@ -17114,10 +17111,10 @@
         <v>13</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D392" s="0" t="s">
         <v>67</v>
@@ -17152,10 +17149,10 @@
         <v>13</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="D393" s="0" t="s">
         <v>97</v>
@@ -17190,10 +17187,10 @@
         <v>13</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D394" s="0" t="s">
         <v>154</v>
@@ -17228,10 +17225,10 @@
         <v>13</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="D395" s="0" t="s">
         <v>97</v>
@@ -17263,10 +17260,10 @@
         <v>13</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D396" s="0" t="s">
         <v>107</v>
@@ -17298,13 +17295,13 @@
         <v>13</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D397" s="0" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E397" s="0" t="n">
         <v>20</v>
@@ -17333,10 +17330,10 @@
         <v>13</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="D398" s="0" t="s">
         <v>25</v>
@@ -17368,10 +17365,10 @@
         <v>13</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D399" s="0" t="s">
         <v>25</v>
@@ -17406,10 +17403,10 @@
         <v>13</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="D400" s="0" t="s">
         <v>67</v>
@@ -17444,10 +17441,10 @@
         <v>13</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="D401" s="0" t="s">
         <v>107</v>
@@ -17482,10 +17479,10 @@
         <v>13</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="D402" s="0" t="s">
         <v>97</v>
@@ -17520,10 +17517,10 @@
         <v>13</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="D403" s="0" t="s">
         <v>154</v>
@@ -17558,10 +17555,10 @@
         <v>13</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="D404" s="0" t="s">
         <v>25</v>
@@ -17596,10 +17593,10 @@
         <v>13</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D405" s="0" t="s">
         <v>79</v>
@@ -17634,10 +17631,10 @@
         <v>13</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="D406" s="0" t="s">
         <v>131</v>
@@ -17672,10 +17669,10 @@
         <v>13</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="D407" s="0" t="s">
         <v>25</v>
@@ -17710,10 +17707,10 @@
         <v>13</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="D408" s="0" t="s">
         <v>159</v>
@@ -17748,10 +17745,10 @@
         <v>13</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D409" s="0" t="s">
         <v>172</v>
@@ -17786,10 +17783,10 @@
         <v>13</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D410" s="0" t="s">
         <v>148</v>
@@ -17824,13 +17821,13 @@
         <v>13</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="D411" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E411" s="0" t="n">
         <v>16</v>
@@ -17842,13 +17839,13 @@
         <v>18</v>
       </c>
       <c r="H411" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I411" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J411" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L411" s="0" t="s">
         <v>20</v>
@@ -17862,10 +17859,10 @@
         <v>13</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="D412" s="0" t="s">
         <v>25</v>
@@ -17897,10 +17894,10 @@
         <v>13</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="D413" s="0" t="s">
         <v>74</v>
@@ -17932,10 +17929,10 @@
         <v>13</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="D414" s="0" t="s">
         <v>82</v>
@@ -17967,10 +17964,10 @@
         <v>13</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="D415" s="0" t="s">
         <v>67</v>
@@ -18002,10 +17999,10 @@
         <v>13</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="D416" s="0" t="s">
         <v>97</v>
@@ -18040,10 +18037,10 @@
         <v>13</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="D417" s="0" t="s">
         <v>154</v>
@@ -18078,10 +18075,10 @@
         <v>13</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D418" s="0" t="s">
         <v>97</v>
@@ -18116,10 +18113,10 @@
         <v>13</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="D419" s="0" t="s">
         <v>154</v>
@@ -18154,10 +18151,10 @@
         <v>13</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="D420" s="0" t="s">
         <v>139</v>
@@ -18192,10 +18189,10 @@
         <v>13</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="D421" s="0" t="s">
         <v>55</v>
@@ -18230,13 +18227,13 @@
         <v>13</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="D422" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E422" s="0" t="n">
         <v>4</v>
@@ -18248,13 +18245,13 @@
         <v>18</v>
       </c>
       <c r="H422" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I422" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J422" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L422" s="0" t="s">
         <v>20</v>
@@ -18268,10 +18265,10 @@
         <v>13</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="D423" s="0" t="s">
         <v>25</v>
@@ -18306,10 +18303,10 @@
         <v>13</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="D424" s="0" t="s">
         <v>62</v>
@@ -18344,13 +18341,13 @@
         <v>13</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="D425" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E425" s="0" t="n">
         <v>6</v>
@@ -18362,10 +18359,10 @@
         <v>18</v>
       </c>
       <c r="H425" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I425" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J425" s="0" t="s">
         <v>27</v>
@@ -18382,10 +18379,10 @@
         <v>13</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="D426" s="0" t="s">
         <v>115</v>
@@ -18420,10 +18417,10 @@
         <v>13</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="D427" s="0" t="s">
         <v>25</v>
@@ -18458,10 +18455,10 @@
         <v>13</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D428" s="0" t="s">
         <v>79</v>
@@ -18496,10 +18493,10 @@
         <v>13</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="D429" s="0" t="s">
         <v>97</v>
@@ -18531,10 +18528,10 @@
         <v>13</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D430" s="0" t="s">
         <v>165</v>
@@ -18566,10 +18563,10 @@
         <v>13</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="D431" s="0" t="s">
         <v>25</v>
@@ -18601,13 +18598,13 @@
         <v>13</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D432" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E432" s="0" t="n">
         <v>9</v>
@@ -18619,13 +18616,13 @@
         <v>18</v>
       </c>
       <c r="H432" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I432" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J432" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L432" s="0" t="s">
         <v>20</v>
@@ -18639,10 +18636,10 @@
         <v>13</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D433" s="0" t="s">
         <v>67</v>
@@ -18677,10 +18674,10 @@
         <v>13</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="D434" s="0" t="s">
         <v>97</v>
@@ -18715,10 +18712,10 @@
         <v>13</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D435" s="0" t="s">
         <v>154</v>
@@ -18753,10 +18750,10 @@
         <v>13</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="D436" s="0" t="s">
         <v>260</v>
@@ -18780,7 +18777,7 @@
         <v>262</v>
       </c>
       <c r="L436" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M436" s="0" t="n">
         <v>1</v>
@@ -18791,10 +18788,10 @@
         <v>13</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="D437" s="0" t="s">
         <v>62</v>
@@ -18829,10 +18826,10 @@
         <v>13</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="D438" s="0" t="s">
         <v>74</v>
@@ -18867,10 +18864,10 @@
         <v>13</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="D439" s="0" t="s">
         <v>175</v>
@@ -18905,10 +18902,10 @@
         <v>13</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="D440" s="0" t="s">
         <v>25</v>
@@ -18943,10 +18940,10 @@
         <v>13</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="D441" s="0" t="s">
         <v>79</v>
@@ -18981,10 +18978,10 @@
         <v>13</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="D442" s="0" t="s">
         <v>25</v>
@@ -19019,10 +19016,10 @@
         <v>13</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C443" s="1" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D443" s="0" t="s">
         <v>79</v>
@@ -19057,10 +19054,10 @@
         <v>13</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="D444" s="0" t="s">
         <v>25</v>
@@ -19092,10 +19089,10 @@
         <v>13</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="D445" s="0" t="s">
         <v>74</v>
@@ -19127,10 +19124,10 @@
         <v>13</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D446" s="0" t="s">
         <v>139</v>
@@ -19162,10 +19159,10 @@
         <v>13</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="D447" s="0" t="s">
         <v>55</v>
@@ -19197,10 +19194,10 @@
         <v>13</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="D448" s="0" t="s">
         <v>172</v>
@@ -19232,10 +19229,10 @@
         <v>13</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="D449" s="0" t="s">
         <v>90</v>
@@ -19259,7 +19256,7 @@
         <v>93</v>
       </c>
       <c r="L449" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M449" s="0" t="n">
         <v>1</v>
@@ -19270,10 +19267,10 @@
         <v>13</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D450" s="0" t="s">
         <v>159</v>
@@ -19308,10 +19305,10 @@
         <v>13</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="D451" s="0" t="s">
         <v>67</v>
@@ -19346,10 +19343,10 @@
         <v>13</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="D452" s="0" t="s">
         <v>97</v>
@@ -19384,10 +19381,10 @@
         <v>13</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="D453" s="0" t="s">
         <v>154</v>
@@ -19422,10 +19419,10 @@
         <v>13</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D454" s="0" t="s">
         <v>90</v>
@@ -19449,7 +19446,7 @@
         <v>93</v>
       </c>
       <c r="L454" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M454" s="0" t="n">
         <v>1</v>
@@ -19460,10 +19457,10 @@
         <v>13</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="D455" s="0" t="s">
         <v>25</v>
@@ -19498,10 +19495,10 @@
         <v>13</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="D456" s="0" t="s">
         <v>97</v>
@@ -19536,10 +19533,10 @@
         <v>13</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="D457" s="0" t="s">
         <v>97</v>
@@ -19574,13 +19571,13 @@
         <v>13</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="D458" s="0" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E458" s="0" t="n">
         <v>11</v>
@@ -19592,10 +19589,10 @@
         <v>18</v>
       </c>
       <c r="H458" s="0" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="I458" s="0" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="J458" s="0" t="s">
         <v>93</v>
@@ -19612,10 +19609,10 @@
         <v>13</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="D459" s="0" t="s">
         <v>184</v>
@@ -19650,10 +19647,10 @@
         <v>13</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="D460" s="0" t="s">
         <v>168</v>
@@ -19685,10 +19682,10 @@
         <v>13</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D461" s="0" t="s">
         <v>184</v>
@@ -19720,10 +19717,10 @@
         <v>13</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="D462" s="0" t="s">
         <v>25</v>
@@ -19755,13 +19752,13 @@
         <v>13</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="D463" s="0" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E463" s="0" t="n">
         <v>22</v>
@@ -19790,10 +19787,10 @@
         <v>13</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="C464" s="1" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="D464" s="0" t="s">
         <v>25</v>
@@ -19825,10 +19822,10 @@
         <v>13</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D465" s="0" t="s">
         <v>74</v>
@@ -19846,7 +19843,7 @@
         <v>75</v>
       </c>
       <c r="I465" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="J465" s="0" t="s">
         <v>77</v>
@@ -19860,10 +19857,10 @@
         <v>13</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="D466" s="0" t="s">
         <v>159</v>
@@ -19895,10 +19892,10 @@
         <v>13</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C467" s="1" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="D467" s="0" t="s">
         <v>25</v>
@@ -19922,7 +19919,7 @@
         <v>27</v>
       </c>
       <c r="L467" s="0" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="M467" s="0" t="n">
         <v>1</v>
@@ -19933,10 +19930,10 @@
         <v>13</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="C468" s="1" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D468" s="0" t="s">
         <v>168</v>
@@ -19968,10 +19965,10 @@
         <v>13</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="D469" s="0" t="s">
         <v>184</v>
@@ -20003,10 +20000,10 @@
         <v>13</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="C470" s="1" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="D470" s="0" t="s">
         <v>25</v>
@@ -20038,10 +20035,10 @@
         <v>13</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="D471" s="0" t="s">
         <v>79</v>
@@ -20073,10 +20070,10 @@
         <v>13</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="D472" s="0" t="s">
         <v>55</v>
@@ -20108,10 +20105,10 @@
         <v>13</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D473" s="0" t="s">
         <v>159</v>
@@ -20143,10 +20140,10 @@
         <v>13</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="D474" s="0" t="s">
         <v>85</v>
@@ -20178,10 +20175,10 @@
         <v>13</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C475" s="1" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="D475" s="0" t="s">
         <v>168</v>
@@ -20213,10 +20210,10 @@
         <v>13</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C476" s="1" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="D476" s="0" t="s">
         <v>184</v>
@@ -20248,10 +20245,10 @@
         <v>13</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="C477" s="1" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D477" s="0" t="s">
         <v>25</v>
@@ -20283,10 +20280,10 @@
         <v>13</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="D478" s="0" t="s">
         <v>175</v>
@@ -20318,13 +20315,13 @@
         <v>13</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="D479" s="0" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E479" s="0" t="n">
         <v>8</v>
@@ -20339,7 +20336,7 @@
         <v>26</v>
       </c>
       <c r="I479" s="0" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="J479" s="0" t="s">
         <v>27</v>
@@ -20353,10 +20350,10 @@
         <v>13</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D480" s="0" t="s">
         <v>62</v>
@@ -20388,10 +20385,10 @@
         <v>13</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="D481" s="0" t="s">
         <v>97</v>
@@ -20423,10 +20420,10 @@
         <v>13</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="D482" s="0" t="s">
         <v>82</v>
@@ -20458,13 +20455,13 @@
         <v>13</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="D483" s="0" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E483" s="0" t="n">
         <v>8</v>
@@ -20476,10 +20473,10 @@
         <v>59</v>
       </c>
       <c r="H483" s="0" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I483" s="0" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="J483" s="0" t="s">
         <v>27</v>
@@ -20493,10 +20490,10 @@
         <v>13</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="D484" s="0" t="s">
         <v>172</v>
@@ -20528,10 +20525,10 @@
         <v>13</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="D485" s="0" t="s">
         <v>25</v>
@@ -20563,10 +20560,10 @@
         <v>13</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="D486" s="0" t="s">
         <v>25</v>
@@ -20601,13 +20598,13 @@
         <v>13</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D487" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E487" s="0" t="n">
         <v>10</v>
@@ -20619,13 +20616,13 @@
         <v>18</v>
       </c>
       <c r="H487" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I487" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J487" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L487" s="0" t="s">
         <v>20</v>
@@ -20639,10 +20636,10 @@
         <v>13</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="D488" s="0" t="s">
         <v>74</v>
@@ -20677,10 +20674,10 @@
         <v>13</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D489" s="0" t="s">
         <v>25</v>
@@ -20712,10 +20709,10 @@
         <v>13</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D490" s="0" t="s">
         <v>74</v>
@@ -20747,10 +20744,10 @@
         <v>13</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="D491" s="0" t="s">
         <v>107</v>
@@ -20782,10 +20779,10 @@
         <v>13</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="D492" s="0" t="s">
         <v>72</v>
@@ -20817,10 +20814,10 @@
         <v>13</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D493" s="0" t="s">
         <v>175</v>
@@ -20852,10 +20849,10 @@
         <v>13</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="D494" s="0" t="s">
         <v>175</v>
@@ -20890,10 +20887,10 @@
         <v>13</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D495" s="0" t="s">
         <v>25</v>
@@ -20928,13 +20925,13 @@
         <v>13</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D496" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E496" s="0" t="n">
         <v>12</v>
@@ -20946,16 +20943,16 @@
         <v>18</v>
       </c>
       <c r="H496" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I496" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J496" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L496" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M496" s="0" t="n">
         <v>1</v>
@@ -20966,10 +20963,10 @@
         <v>13</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C497" s="1" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D497" s="0" t="s">
         <v>148</v>
@@ -21004,10 +21001,10 @@
         <v>13</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="C498" s="1" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="D498" s="0" t="s">
         <v>115</v>
@@ -21042,10 +21039,10 @@
         <v>13</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C499" s="1" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="D499" s="0" t="s">
         <v>82</v>
@@ -21077,10 +21074,10 @@
         <v>13</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C500" s="1" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="D500" s="0" t="s">
         <v>139</v>
@@ -21112,10 +21109,10 @@
         <v>13</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C501" s="1" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="D501" s="0" t="s">
         <v>55</v>
@@ -21147,13 +21144,13 @@
         <v>13</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="D502" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E502" s="0" t="n">
         <v>16</v>
@@ -21165,10 +21162,10 @@
         <v>59</v>
       </c>
       <c r="H502" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I502" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="J502" s="0" t="s">
         <v>27</v>
@@ -21182,10 +21179,10 @@
         <v>13</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C503" s="1" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="D503" s="0" t="s">
         <v>25</v>
@@ -21217,10 +21214,10 @@
         <v>13</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C504" s="1" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="D504" s="0" t="s">
         <v>62</v>
@@ -21252,10 +21249,10 @@
         <v>13</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="D505" s="0" t="s">
         <v>25</v>
@@ -21287,10 +21284,10 @@
         <v>13</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="D506" s="0" t="s">
         <v>67</v>
@@ -21322,10 +21319,10 @@
         <v>13</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="D507" s="0" t="s">
         <v>72</v>
@@ -21357,10 +21354,10 @@
         <v>13</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="C508" s="1" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="D508" s="0" t="s">
         <v>97</v>
@@ -21392,10 +21389,10 @@
         <v>13</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C509" s="1" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="D509" s="0" t="s">
         <v>25</v>
@@ -21427,10 +21424,10 @@
         <v>13</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="C510" s="1" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="D510" s="0" t="s">
         <v>74</v>
@@ -21462,10 +21459,10 @@
         <v>13</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D511" s="0" t="s">
         <v>79</v>
@@ -21497,13 +21494,13 @@
         <v>13</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C512" s="1" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="D512" s="0" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="E512" s="0" t="n">
         <v>11</v>
@@ -21515,13 +21512,13 @@
         <v>59</v>
       </c>
       <c r="H512" s="0" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="I512" s="0" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="J512" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M512" s="0" t="n">
         <v>1</v>
@@ -21532,10 +21529,10 @@
         <v>13</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C513" s="1" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D513" s="0" t="s">
         <v>25</v>
@@ -21567,13 +21564,13 @@
         <v>13</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C514" s="1" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="D514" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E514" s="0" t="n">
         <v>14</v>
@@ -21585,13 +21582,13 @@
         <v>18</v>
       </c>
       <c r="H514" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I514" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J514" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L514" s="0" t="s">
         <v>35</v>
@@ -21605,10 +21602,10 @@
         <v>13</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="C515" s="1" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D515" s="0" t="s">
         <v>97</v>
@@ -21643,10 +21640,10 @@
         <v>13</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="C516" s="1" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D516" s="0" t="s">
         <v>168</v>
@@ -21678,10 +21675,10 @@
         <v>13</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C517" s="1" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D517" s="0" t="s">
         <v>184</v>
@@ -21713,10 +21710,10 @@
         <v>13</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="C518" s="1" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D518" s="0" t="s">
         <v>25</v>
@@ -21748,10 +21745,10 @@
         <v>13</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C519" s="1" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D519" s="0" t="s">
         <v>100</v>
@@ -21783,10 +21780,10 @@
         <v>13</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C520" s="1" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D520" s="0" t="s">
         <v>72</v>
@@ -21818,13 +21815,13 @@
         <v>13</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C521" s="1" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="D521" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E521" s="0" t="n">
         <v>8</v>
@@ -21836,13 +21833,13 @@
         <v>18</v>
       </c>
       <c r="H521" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I521" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J521" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L521" s="0" t="s">
         <v>20</v>
@@ -21856,10 +21853,10 @@
         <v>13</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D522" s="0" t="s">
         <v>139</v>
@@ -21894,10 +21891,10 @@
         <v>13</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C523" s="1" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="D523" s="0" t="s">
         <v>72</v>
@@ -21921,7 +21918,7 @@
         <v>27</v>
       </c>
       <c r="L523" s="0" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M523" s="0" t="n">
         <v>1</v>
@@ -21932,13 +21929,13 @@
         <v>13</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C524" s="1" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="D524" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E524" s="0" t="n">
         <v>6</v>
@@ -21950,13 +21947,13 @@
         <v>18</v>
       </c>
       <c r="H524" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I524" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J524" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L524" s="0" t="s">
         <v>20</v>
@@ -21970,10 +21967,10 @@
         <v>13</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C525" s="1" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="D525" s="0" t="s">
         <v>25</v>
@@ -22005,10 +22002,10 @@
         <v>13</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="C526" s="1" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="D526" s="0" t="s">
         <v>25</v>
@@ -22040,10 +22037,10 @@
         <v>13</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C527" s="1" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D527" s="0" t="s">
         <v>74</v>
@@ -22075,10 +22072,10 @@
         <v>13</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C528" s="1" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="D528" s="0" t="s">
         <v>90</v>
@@ -22110,10 +22107,10 @@
         <v>13</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="C529" s="1" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="D529" s="0" t="s">
         <v>67</v>
@@ -22145,10 +22142,10 @@
         <v>13</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D530" s="0" t="s">
         <v>74</v>
@@ -22183,10 +22180,10 @@
         <v>13</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C531" s="1" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="D531" s="0" t="s">
         <v>107</v>
@@ -22221,10 +22218,10 @@
         <v>13</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="C532" s="1" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="D532" s="0" t="s">
         <v>79</v>
@@ -22256,10 +22253,10 @@
         <v>13</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C533" s="1" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="D533" s="0" t="s">
         <v>97</v>
@@ -22291,10 +22288,10 @@
         <v>13</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="D534" s="0" t="s">
         <v>148</v>
@@ -22326,10 +22323,10 @@
         <v>13</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="C535" s="1" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="D535" s="0" t="s">
         <v>82</v>
@@ -22361,10 +22358,10 @@
         <v>13</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="C536" s="1" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="D536" s="0" t="s">
         <v>172</v>
@@ -22396,10 +22393,10 @@
         <v>13</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="D537" s="0" t="s">
         <v>25</v>
@@ -22434,10 +22431,10 @@
         <v>13</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C538" s="1" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="D538" s="0" t="s">
         <v>85</v>
@@ -22472,10 +22469,10 @@
         <v>13</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="C539" s="1" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="D539" s="0" t="s">
         <v>172</v>
@@ -22510,10 +22507,10 @@
         <v>13</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="C540" s="1" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="D540" s="0" t="s">
         <v>25</v>
@@ -22545,10 +22542,10 @@
         <v>13</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C541" s="1" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="D541" s="0" t="s">
         <v>74</v>
@@ -22566,7 +22563,7 @@
         <v>75</v>
       </c>
       <c r="I541" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="J541" s="0" t="s">
         <v>77</v>
@@ -22580,10 +22577,10 @@
         <v>13</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="C542" s="1" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="D542" s="0" t="s">
         <v>131</v>
@@ -22615,10 +22612,10 @@
         <v>13</v>
       </c>
       <c r="B543" s="1" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C543" s="1" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="D543" s="0" t="s">
         <v>40</v>
@@ -22636,7 +22633,7 @@
         <v>41</v>
       </c>
       <c r="I543" s="0" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="J543" s="0" t="s">
         <v>19</v>
@@ -22650,10 +22647,10 @@
         <v>13</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="D544" s="0" t="s">
         <v>72</v>
@@ -22685,13 +22682,13 @@
         <v>13</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C545" s="1" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="D545" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E545" s="0" t="n">
         <v>6</v>
@@ -22703,10 +22700,10 @@
         <v>18</v>
       </c>
       <c r="H545" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I545" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J545" s="0" t="s">
         <v>27</v>
@@ -22723,10 +22720,10 @@
         <v>13</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="C546" s="1" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="D546" s="0" t="s">
         <v>168</v>
@@ -22758,10 +22755,10 @@
         <v>13</v>
       </c>
       <c r="B547" s="1" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C547" s="1" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="D547" s="0" t="s">
         <v>184</v>
@@ -22793,10 +22790,10 @@
         <v>13</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C548" s="1" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="D548" s="0" t="s">
         <v>25</v>
@@ -22828,13 +22825,13 @@
         <v>13</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="C549" s="1" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="D549" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E549" s="0" t="n">
         <v>14</v>
@@ -22846,10 +22843,10 @@
         <v>59</v>
       </c>
       <c r="H549" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I549" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="J549" s="0" t="s">
         <v>27</v>
@@ -22863,10 +22860,10 @@
         <v>13</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C550" s="1" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="D550" s="0" t="s">
         <v>72</v>
@@ -22898,10 +22895,10 @@
         <v>13</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="D551" s="0" t="s">
         <v>97</v>
@@ -22936,10 +22933,10 @@
         <v>13</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="C552" s="1" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="D552" s="0" t="s">
         <v>97</v>
@@ -22971,10 +22968,10 @@
         <v>13</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C553" s="1" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="D553" s="0" t="s">
         <v>107</v>
@@ -23006,10 +23003,10 @@
         <v>13</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C554" s="1" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="D554" s="0" t="s">
         <v>62</v>
@@ -23041,10 +23038,10 @@
         <v>13</v>
       </c>
       <c r="B555" s="1" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C555" s="1" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="D555" s="0" t="s">
         <v>67</v>
@@ -23076,10 +23073,10 @@
         <v>13</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="C556" s="1" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="D556" s="0" t="s">
         <v>25</v>
@@ -23111,13 +23108,13 @@
         <v>13</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C557" s="1" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="D557" s="0" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="E557" s="0" t="n">
         <v>5</v>
@@ -23132,7 +23129,7 @@
         <v>63</v>
       </c>
       <c r="I557" s="0" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="J557" s="0" t="s">
         <v>65</v>
@@ -23149,10 +23146,10 @@
         <v>13</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="D558" s="0" t="s">
         <v>184</v>
@@ -23187,10 +23184,10 @@
         <v>13</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="C559" s="1" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="D559" s="0" t="s">
         <v>168</v>
@@ -23222,10 +23219,10 @@
         <v>13</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C560" s="1" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="D560" s="0" t="s">
         <v>184</v>
@@ -23257,10 +23254,10 @@
         <v>13</v>
       </c>
       <c r="B561" s="1" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="C561" s="1" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D561" s="0" t="s">
         <v>25</v>
@@ -23292,10 +23289,10 @@
         <v>13</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="C562" s="1" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="D562" s="0" t="s">
         <v>67</v>
@@ -23327,10 +23324,10 @@
         <v>13</v>
       </c>
       <c r="B563" s="1" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="C563" s="1" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="D563" s="0" t="s">
         <v>72</v>
@@ -23362,10 +23359,10 @@
         <v>13</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="C564" s="1" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="D564" s="0" t="s">
         <v>25</v>
@@ -23400,13 +23397,13 @@
         <v>13</v>
       </c>
       <c r="B565" s="1" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="C565" s="1" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="D565" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E565" s="0" t="n">
         <v>8</v>
@@ -23418,13 +23415,13 @@
         <v>18</v>
       </c>
       <c r="H565" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I565" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J565" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L565" s="0" t="s">
         <v>20</v>
@@ -23438,13 +23435,13 @@
         <v>13</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="C566" s="1" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="D566" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E566" s="0" t="n">
         <v>4</v>
@@ -23456,13 +23453,13 @@
         <v>18</v>
       </c>
       <c r="H566" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I566" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J566" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L566" s="0" t="s">
         <v>20</v>
@@ -23476,10 +23473,10 @@
         <v>13</v>
       </c>
       <c r="B567" s="1" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C567" s="1" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="D567" s="0" t="s">
         <v>25</v>
@@ -23511,10 +23508,10 @@
         <v>13</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D568" s="0" t="s">
         <v>74</v>
@@ -23532,7 +23529,7 @@
         <v>75</v>
       </c>
       <c r="I568" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="J568" s="0" t="s">
         <v>77</v>
@@ -23546,10 +23543,10 @@
         <v>13</v>
       </c>
       <c r="B569" s="1" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="C569" s="1" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="D569" s="0" t="s">
         <v>82</v>
@@ -23581,10 +23578,10 @@
         <v>13</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C570" s="1" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D570" s="0" t="s">
         <v>139</v>
@@ -23616,10 +23613,10 @@
         <v>13</v>
       </c>
       <c r="B571" s="1" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="C571" s="1" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="D571" s="0" t="s">
         <v>55</v>
@@ -23651,10 +23648,10 @@
         <v>13</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D572" s="0" t="s">
         <v>90</v>
@@ -23686,10 +23683,10 @@
         <v>13</v>
       </c>
       <c r="B573" s="1" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="C573" s="1" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="D573" s="0" t="s">
         <v>115</v>
@@ -23724,10 +23721,10 @@
         <v>13</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D574" s="0" t="s">
         <v>154</v>
@@ -23762,10 +23759,10 @@
         <v>13</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="D575" s="0" t="s">
         <v>25</v>
@@ -23800,10 +23797,10 @@
         <v>13</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="C576" s="1" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="D576" s="0" t="s">
         <v>25</v>
@@ -23838,10 +23835,10 @@
         <v>13</v>
       </c>
       <c r="B577" s="1" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C577" s="1" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="D577" s="0" t="s">
         <v>79</v>
@@ -23873,10 +23870,10 @@
         <v>13</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C578" s="1" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="D578" s="0" t="s">
         <v>97</v>
@@ -23908,10 +23905,10 @@
         <v>13</v>
       </c>
       <c r="B579" s="1" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C579" s="1" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="D579" s="0" t="s">
         <v>90</v>
@@ -23943,13 +23940,13 @@
         <v>13</v>
       </c>
       <c r="B580" s="1" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="D580" s="0" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E580" s="0" t="n">
         <v>9</v>
@@ -23961,10 +23958,10 @@
         <v>59</v>
       </c>
       <c r="H580" s="0" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="I580" s="0" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="J580" s="0" t="s">
         <v>57</v>
@@ -23978,10 +23975,10 @@
         <v>13</v>
       </c>
       <c r="B581" s="1" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C581" s="1" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="D581" s="0" t="s">
         <v>74</v>
@@ -23999,7 +23996,7 @@
         <v>75</v>
       </c>
       <c r="I581" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="J581" s="0" t="s">
         <v>77</v>
@@ -24013,10 +24010,10 @@
         <v>13</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="D582" s="0" t="s">
         <v>25</v>
@@ -24048,10 +24045,10 @@
         <v>13</v>
       </c>
       <c r="B583" s="1" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="D583" s="0" t="s">
         <v>168</v>
@@ -24086,10 +24083,10 @@
         <v>13</v>
       </c>
       <c r="B584" s="1" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C584" s="1" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="D584" s="0" t="s">
         <v>184</v>
@@ -24124,10 +24121,10 @@
         <v>13</v>
       </c>
       <c r="B585" s="1" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="C585" s="1" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="D585" s="0" t="s">
         <v>168</v>
@@ -24159,10 +24156,10 @@
         <v>13</v>
       </c>
       <c r="B586" s="1" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="C586" s="1" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="D586" s="0" t="s">
         <v>184</v>
@@ -24194,10 +24191,10 @@
         <v>13</v>
       </c>
       <c r="B587" s="1" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="C587" s="1" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="D587" s="0" t="s">
         <v>25</v>
@@ -24229,10 +24226,10 @@
         <v>13</v>
       </c>
       <c r="B588" s="1" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="C588" s="1" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="D588" s="0" t="s">
         <v>67</v>
@@ -24264,10 +24261,10 @@
         <v>13</v>
       </c>
       <c r="B589" s="1" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="C589" s="1" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="D589" s="0" t="s">
         <v>285</v>
@@ -24282,13 +24279,13 @@
         <v>59</v>
       </c>
       <c r="H589" s="0" t="s">
-        <v>927</v>
+        <v>286</v>
       </c>
       <c r="I589" s="0" t="s">
-        <v>928</v>
+        <v>287</v>
       </c>
       <c r="J589" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M589" s="0" t="n">
         <v>1</v>
@@ -24299,10 +24296,10 @@
         <v>13</v>
       </c>
       <c r="B590" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C590" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D590" s="0" t="s">
         <v>25</v>
@@ -24334,10 +24331,10 @@
         <v>13</v>
       </c>
       <c r="B591" s="1" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C591" s="1" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D591" s="0" t="s">
         <v>74</v>
@@ -24355,7 +24352,7 @@
         <v>75</v>
       </c>
       <c r="I591" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="J591" s="0" t="s">
         <v>77</v>
@@ -24369,10 +24366,10 @@
         <v>13</v>
       </c>
       <c r="B592" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C592" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D592" s="0" t="s">
         <v>85</v>
@@ -24404,13 +24401,13 @@
         <v>13</v>
       </c>
       <c r="B593" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C593" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D593" s="0" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E593" s="0" t="n">
         <v>8</v>
@@ -24422,13 +24419,13 @@
         <v>59</v>
       </c>
       <c r="H593" s="0" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="I593" s="0" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J593" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M593" s="0" t="n">
         <v>1</v>
@@ -24439,13 +24436,13 @@
         <v>13</v>
       </c>
       <c r="B594" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C594" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D594" s="0" t="s">
-        <v>934</v>
+        <v>298</v>
       </c>
       <c r="E594" s="0" t="n">
         <v>14</v>
@@ -24457,10 +24454,10 @@
         <v>59</v>
       </c>
       <c r="H594" s="0" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I594" s="0" t="s">
-        <v>935</v>
+        <v>300</v>
       </c>
       <c r="J594" s="0" t="s">
         <v>34</v>
@@ -24474,10 +24471,10 @@
         <v>13</v>
       </c>
       <c r="B595" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="C595" s="1" t="s">
         <v>936</v>
-      </c>
-      <c r="C595" s="1" t="s">
-        <v>937</v>
       </c>
       <c r="D595" s="0" t="s">
         <v>168</v>
@@ -24512,10 +24509,10 @@
         <v>13</v>
       </c>
       <c r="B596" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="C596" s="1" t="s">
         <v>938</v>
-      </c>
-      <c r="C596" s="1" t="s">
-        <v>939</v>
       </c>
       <c r="D596" s="0" t="s">
         <v>184</v>
@@ -24550,10 +24547,10 @@
         <v>13</v>
       </c>
       <c r="B597" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C597" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D597" s="0" t="s">
         <v>168</v>
@@ -24585,10 +24582,10 @@
         <v>13</v>
       </c>
       <c r="B598" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C598" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D598" s="0" t="s">
         <v>184</v>
@@ -24620,10 +24617,10 @@
         <v>13</v>
       </c>
       <c r="B599" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C599" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D599" s="0" t="s">
         <v>25</v>
@@ -24655,10 +24652,10 @@
         <v>13</v>
       </c>
       <c r="B600" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C600" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D600" s="0" t="s">
         <v>165</v>
@@ -24690,10 +24687,10 @@
         <v>13</v>
       </c>
       <c r="B601" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C601" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D601" s="0" t="s">
         <v>97</v>
@@ -24725,10 +24722,10 @@
         <v>13</v>
       </c>
       <c r="B602" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C602" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="D602" s="0" t="s">
         <v>107</v>
@@ -24760,10 +24757,10 @@
         <v>13</v>
       </c>
       <c r="B603" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C603" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="D603" s="0" t="s">
         <v>148</v>
@@ -24795,10 +24792,10 @@
         <v>13</v>
       </c>
       <c r="B604" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="C604" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="D604" s="0" t="s">
         <v>82</v>
@@ -24830,10 +24827,10 @@
         <v>13</v>
       </c>
       <c r="B605" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C605" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="D605" s="0" t="s">
         <v>175</v>
@@ -24865,10 +24862,10 @@
         <v>13</v>
       </c>
       <c r="B606" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C606" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D606" s="0" t="s">
         <v>25</v>
@@ -24900,10 +24897,10 @@
         <v>13</v>
       </c>
       <c r="B607" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C607" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D607" s="0" t="s">
         <v>165</v>
@@ -24935,10 +24932,10 @@
         <v>13</v>
       </c>
       <c r="B608" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="C608" s="1" t="s">
         <v>951</v>
-      </c>
-      <c r="C608" s="1" t="s">
-        <v>952</v>
       </c>
       <c r="D608" s="0" t="s">
         <v>97</v>
@@ -24973,10 +24970,10 @@
         <v>13</v>
       </c>
       <c r="B609" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="C609" s="1" t="s">
         <v>953</v>
-      </c>
-      <c r="C609" s="1" t="s">
-        <v>954</v>
       </c>
       <c r="D609" s="0" t="s">
         <v>154</v>
@@ -25011,10 +25008,10 @@
         <v>13</v>
       </c>
       <c r="B610" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="C610" s="1" t="s">
         <v>955</v>
-      </c>
-      <c r="C610" s="1" t="s">
-        <v>956</v>
       </c>
       <c r="D610" s="0" t="s">
         <v>184</v>
@@ -25049,10 +25046,10 @@
         <v>13</v>
       </c>
       <c r="B611" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="C611" s="1" t="s">
         <v>957</v>
-      </c>
-      <c r="C611" s="1" t="s">
-        <v>958</v>
       </c>
       <c r="D611" s="0" t="s">
         <v>25</v>
